--- a/vse-loti/339433992/spec-339433992.xlsx
+++ b/vse-loti/339433992/spec-339433992.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +60,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,14 +437,14 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,14 +505,14 @@
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Источник: 852557330.doc</t>
+          <t>Источник: 852557331.txt</t>
         </is>
       </c>
     </row>

--- a/vse-loti/339433992/spec-339433992.xlsx
+++ b/vse-loti/339433992/spec-339433992.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -60,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -443,8 +440,6 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,25 +470,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (без НДС)</t>
+          <t>Стоимость (без НДС)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Цена за ед. (с НДС)</t>
+          <t>Цена за т (без НДС)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Стоимость (без НДС)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -504,9 +489,6 @@
         <is>
           <t>ИТОГО</t>
         </is>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="5">
